--- a/docs/最新版/02_管理シート/フェーズ別収益モデル.xlsx
+++ b/docs/最新版/02_管理シート/フェーズ別収益モデル.xlsx
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -132,9 +132,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -522,14 +519,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ぺいほーむ フェーズ別 収益モデル</t>
+          <t>ぺいほーむ フェーズ別 収益モデル (全員同一料金)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Phase x 機能 x 収益モデル x 10社優遇 の対応表</t>
+          <t>10社料金優遇ゼロ。差別化はAI診断での優先送客のみ</t>
         </is>
       </c>
     </row>
@@ -563,7 +560,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Phase 1〜5 の料金プランと10社優遇</t>
+          <t>Phase 1〜5 の料金プラン (全員同一)</t>
         </is>
       </c>
     </row>
@@ -614,7 +611,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>10社 + 新規それぞれの適用プラン</t>
+          <t>10社 + 新規それぞれの適用プラン (料金は全員同一)</t>
         </is>
       </c>
     </row>
@@ -648,7 +645,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>見学会予約/撮影/掲載プランの原価と粗利</t>
+          <t>プランごとの粗利率</t>
         </is>
       </c>
     </row>
@@ -667,28 +664,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>① Phase別 料金プラン一覧</t>
+          <t>① Phase別 料金プラン一覧 (全員同一)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>優遇は既存10社に対して常に適用</t>
+          <t>10社と新規で料金は同じ。10社優遇はAI診断優先送客のみ</t>
         </is>
       </c>
     </row>
@@ -705,20 +701,15 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>正規価格</t>
+          <t>料金 (税別)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>10社優遇</t>
+          <t>課金タイミング</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>課金タイミング</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
@@ -742,17 +733,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>初月2ヶ月 無料</t>
+          <t>予約成立時</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>予約成立時</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>5/1-6/30 は運用検証のため無料提供</t>
+          <t>5/1から課金開始、全員同一</t>
         </is>
       </c>
     </row>
@@ -764,27 +750,22 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>成約成果報酬</t>
+          <t>成果報酬</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>3% (上限 ¥500万)</t>
+          <t>−</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>1.5% (上限 ¥250万)</t>
+          <t>−</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>契約成立時</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>建物本体価格の3%</t>
+          <t>Phase 3 から導入</t>
         </is>
       </c>
     </row>
@@ -806,15 +787,10 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>無料</t>
+          <t>−</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>−</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>ユーザー無料</t>
         </is>
@@ -828,7 +804,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>見学会予約</t>
+          <t>見学会予約 (継続)</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -838,17 +814,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>¥25,000/件</t>
+          <t>予約成立時</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>予約成立時</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>以降P2〜P5 常に半額</t>
+          <t>−</t>
         </is>
       </c>
     </row>
@@ -860,59 +831,49 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>成約成果報酬</t>
+          <t>撮影プラン</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>¥150,000/本</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>撮影日</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>契約成立時</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>以降P2〜P5 常に半額</t>
+          <t>ルームツアー撮影+編集+YouTube掲載</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>撮影プラン</t>
+          <t>見学会予約 (継続)</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>¥150,000/本</t>
+          <t>¥50,000/件</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>¥75,000/本</t>
+          <t>予約成立時</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>撮影日</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>ルームツアー撮影 + 編集 + YouTube 掲載</t>
+          <t>−</t>
         </is>
       </c>
     </row>
@@ -924,27 +885,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>見学会予約</t>
+          <t>撮影プラン (継続)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>¥50,000/件</t>
+          <t>¥150,000/本</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>¥25,000/件</t>
+          <t>撮影日</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>予約成立時</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>−</t>
         </is>
       </c>
     </row>
@@ -956,27 +912,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>成約成果報酬</t>
+          <t>月額掲載 ベーシック</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>¥30,000/月</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>毎月月末請求</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>契約成立時</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>物件3件まで</t>
         </is>
       </c>
     </row>
@@ -988,27 +939,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>撮影プラン</t>
+          <t>月額掲載 プロ</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>¥150,000/本</t>
+          <t>¥80,000/月</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>¥75,000/本</t>
+          <t>毎月月末請求</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>撮影日</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>物件無制限+月1本特集枠</t>
         </is>
       </c>
     </row>
@@ -1020,59 +966,49 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>月額掲載 ベーシック</t>
+          <t>成果報酬 3%</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>¥30,000/月</t>
+          <t>契約額の 3% (上限なし)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>初年度 無料</t>
+          <t>契約成立時</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>毎月月末請求</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>物件3件まで掲載</t>
+          <t>★無料相談/AI診断/会員登録済みユーザーの成約のみ</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>月額掲載 プロ</t>
+          <t>見学会予約 (継続)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>¥80,000/月</t>
+          <t>¥50,000/件</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>初年度 ¥40,000/月</t>
+          <t>予約成立時</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>毎月月末請求</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>物件無制限 + 月1本特集枠</t>
+          <t>−</t>
         </is>
       </c>
     </row>
@@ -1084,27 +1020,22 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>見学会予約</t>
+          <t>撮影プラン (継続)</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>¥50,000/件</t>
+          <t>¥150,000/本</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>¥25,000/件</t>
+          <t>撮影日</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>予約成立時</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>−</t>
         </is>
       </c>
     </row>
@@ -1116,27 +1047,22 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>成約成果報酬</t>
+          <t>月額掲載 (継続)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>¥30,000/月 / ¥80,000/月</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>毎月月末請求</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>契約成立時</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>−</t>
         </is>
       </c>
     </row>
@@ -1148,27 +1074,22 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>撮影プラン</t>
+          <t>成果報酬 (継続)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>¥150,000/本</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>¥75,000/本</t>
+          <t>契約成立時</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>撮影日</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>−</t>
         </is>
       </c>
     </row>
@@ -1180,27 +1101,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>月額掲載 ベーシック</t>
+          <t>SaaS ライト</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>¥30,000/月</t>
+          <t>¥50,000/月</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>¥15,000/月</t>
+          <t>毎月月末請求</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>毎月月末請求</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>10社は優遇継続</t>
+          <t>AI質問無制限+インタビュー掲載+月次レポート</t>
         </is>
       </c>
     </row>
@@ -1212,322 +1128,56 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>月額掲載 プロ</t>
+          <t>SaaS プロ</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>¥80,000/月</t>
+          <t>¥150,000/月</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>¥40,000/月</t>
+          <t>毎月月末請求</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>毎月月末請求</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>全機能+専任担当+API連携</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>SaaS ライト</t>
+          <t>全項目継続</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>¥50,000/月</t>
+          <t>正規価格</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>¥25,000/月</t>
+          <t>各タイミング</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>毎月月末請求</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>AI質問無制限 + インタビュー掲載 + 月次レポート</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>SaaS プロ</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>¥150,000/月</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>¥75,000/月</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>毎月月末請求</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>全機能 + 専任担当 + API 連携</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>見学会予約</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>¥50,000/件</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>¥25,000/件</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>予約成立時</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>継続</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>成約成果報酬</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>契約成立時</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>継続</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>撮影プラン</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>¥150,000/本</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>¥75,000/本</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>撮影日</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>継続</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>月額掲載 ベーシック</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>¥30,000/月</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>¥15,000/月</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>毎月月末請求</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>永続優遇</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>月額掲載 プロ</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>¥80,000/月</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>¥40,000/月</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>毎月月末請求</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>永続優遇</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>SaaS ライト</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>¥50,000/月</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr">
-        <is>
-          <t>¥25,000/月</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>毎月月末請求</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>永続優遇</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>SaaS プロ</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>¥150,000/月</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>¥75,000/月</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>毎月月末請求</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>永続優遇</t>
+          <t>全国展開+有料広告投資</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1561,7 +1211,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>どの機能がどの料金プランで提供されるか</t>
+          <t>どの機能がどの料金プランで提供されるか (全員同一)</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1238,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>月額 ベーシック</t>
+          <t>月額ベーシック</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>月額 プロ</t>
+          <t>月額プロ</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2084,7 +1734,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>10社優遇 + 新規11社目以降を含む保守的な想定。Phase2以降は新規開拓により上振れ可能</t>
+          <t>全員同一料金ベース。Phase 3 から成果報酬 (無料相談/AI診断/会員成約対象)</t>
         </is>
       </c>
     </row>
@@ -2106,17 +1756,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>撮影</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>月額掲載</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>成果報酬</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>撮影</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>月額掲載</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2143,32 +1793,32 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
+          <t>¥500,000</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>¥0</t>
+          <t>¥500,000</t>
         </is>
       </c>
     </row>
@@ -2185,12 +1835,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>¥50,000</t>
+          <t>¥750,000</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>¥125,000</t>
+          <t>¥0</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2210,91 +1860,91 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>¥175,000</t>
+          <t>¥750,000</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>¥125,000</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>¥125,000</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>¥75,000</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>¥1,000,000</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>¥150,000</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>¥325,000</t>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>¥1,150,000</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>¥175,000</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>¥125,000</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>¥150,000</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>¥1,250,000</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>¥300,000</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>¥450,000</t>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>¥1,550,000</t>
         </is>
       </c>
     </row>
@@ -2311,22 +1961,22 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>¥225,000</t>
+          <t>¥1,500,000</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>¥250,000</t>
+          <t>¥450,000</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>¥225,000</t>
+          <t>¥90,000</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>¥30,000</t>
+          <t>¥900,000</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -2336,133 +1986,133 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>¥730,000</t>
+          <t>¥2,940,000</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>¥275,000</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>¥250,000</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>¥225,000</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>¥90,000</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>¥1,750,000</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>¥450,000</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>¥150,000</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>¥1,800,000</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>¥0</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>¥840,000</t>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>¥4,150,000</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>¥325,000</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>¥375,000</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>¥2,000,000</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>¥600,000</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>¥240,000</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>¥1,800,000</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>¥0</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>¥4,640,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>12月</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>¥2,250,000</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>¥600,000</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>¥300,000</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>¥180,000</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>¥0</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>¥1,180,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>12月</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>P4</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>¥375,000</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>¥500,000</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>¥300,000</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>¥240,000</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>¥75,000</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>¥1,490,000</t>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>¥2,700,000</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>¥100,000</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>¥5,950,000</t>
         </is>
       </c>
     </row>
@@ -2479,32 +2129,32 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>¥425,000</t>
+          <t>¥2,500,000</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>¥500,000</t>
+          <t>¥750,000</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>¥375,000</t>
+          <t>¥360,000</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>¥270,000</t>
+          <t>¥2,700,000</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>¥150,000</t>
+          <t>¥200,000</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>¥1,720,000</t>
+          <t>¥6,510,000</t>
         </is>
       </c>
     </row>
@@ -2521,32 +2171,32 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>¥475,000</t>
+          <t>¥2,750,000</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>¥625,000</t>
+          <t>¥750,000</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>¥375,000</t>
+          <t>¥390,000</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥3,600,000</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>¥225,000</t>
+          <t>¥450,000</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>¥2,000,000</t>
+          <t>¥7,940,000</t>
         </is>
       </c>
     </row>
@@ -2563,12 +2213,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>¥500,000</t>
+          <t>¥3,000,000</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>¥750,000</t>
+          <t>¥900,000</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -2578,17 +2228,17 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>¥360,000</t>
+          <t>¥3,600,000</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>¥300,000</t>
+          <t>¥550,000</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>¥2,360,000</t>
+          <t>¥8,500,000</t>
         </is>
       </c>
     </row>
@@ -2605,32 +2255,32 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>¥550,000</t>
+          <t>¥3,250,000</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>¥750,000</t>
+          <t>¥900,000</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>¥450,000</t>
+          <t>¥510,000</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>¥390,000</t>
+          <t>¥4,500,000</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>¥375,000</t>
+          <t>¥800,000</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>¥2,515,000</t>
+          <t>¥9,960,000</t>
         </is>
       </c>
     </row>
@@ -2640,15 +2290,15 @@
           <t>年間合計</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr"/>
-      <c r="C17" s="9" t="inlineStr"/>
-      <c r="D17" s="9" t="inlineStr"/>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="9" t="inlineStr"/>
-      <c r="G17" s="9" t="inlineStr"/>
+      <c r="B17" s="8" t="inlineStr"/>
+      <c r="C17" s="8" t="inlineStr"/>
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr"/>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>¥13,785,000</t>
+          <t>¥54,540,000</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2675,23 +2325,22 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>④ 工務店別プラン管理</t>
+          <t>④ 工務店別プラン管理 (全員同一料金)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>社ごとの契約プラン・優遇・期間を管理</t>
+          <t>社ごとの適用プランを管理 (料金は全員同じ)</t>
         </is>
       </c>
     </row>
@@ -2723,472 +2372,417 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>成果報酬</t>
+          <t>撮影</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>撮影プラン</t>
+          <t>月額掲載</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>月額掲載</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
           <t>SaaS</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>(既存10社 #1)</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>2026-04-XX</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>既存優遇</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/件 (P2〜)</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>¥75,000/本 (P2〜)</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>初年度無料 (P3〜)</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/月 (P4〜)</t>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>既存 (優先送客対象)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/件</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>¥150,000/本 (P2〜)</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>¥30,000/月 (P3〜)</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>(既存10社 #2)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>2026-04-XX</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>既存優遇</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/件 (P2〜)</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>¥75,000/本 (P2〜)</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>初年度無料 (P3〜)</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/月 (P4〜)</t>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>既存 (優先送客対象)</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/件</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>¥150,000/本 (P2〜)</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>¥30,000/月 (P3〜)</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>(既存10社 #3)</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>2026-04-XX</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>既存優遇</t>
-        </is>
-      </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/件 (P2〜)</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>¥75,000/本 (P2〜)</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>初年度無料 (P3〜)</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/月 (P4〜)</t>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>既存 (優先送客対象)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/件</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>¥150,000/本 (P2〜)</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>¥30,000/月 (P3〜)</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>(既存10社 #4)</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>2026-04-XX</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>既存優遇</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/件 (P2〜)</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>¥75,000/本 (P2〜)</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>初年度無料 (P3〜)</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/月 (P4〜)</t>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>既存 (優先送客対象)</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/件</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>¥150,000/本 (P2〜)</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>¥30,000/月 (P3〜)</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>(既存10社 #5)</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>2026-04-XX</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>既存優遇</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/件 (P2〜)</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>¥75,000/本 (P2〜)</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>初年度無料 (P3〜)</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/月 (P4〜)</t>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>既存 (優先送客対象)</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/件</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>¥150,000/本 (P2〜)</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>¥30,000/月 (P3〜)</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>(既存10社 #6)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>2026-04-XX</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>既存優遇</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/件 (P2〜)</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>¥75,000/本 (P2〜)</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>初年度無料 (P3〜)</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/月 (P4〜)</t>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>既存 (優先送客対象)</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/件</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>¥150,000/本 (P2〜)</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>¥30,000/月 (P3〜)</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>(既存10社 #7)</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>2026-04-XX</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>既存優遇</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/件 (P2〜)</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>¥75,000/本 (P2〜)</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>初年度無料 (P3〜)</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/月 (P4〜)</t>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>既存 (優先送客対象)</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/件</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>¥150,000/本 (P2〜)</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>¥30,000/月 (P3〜)</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="10" t="n">
+      <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>(既存10社 #8)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>2026-04-XX</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>既存優遇</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/件 (P2〜)</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>¥75,000/本 (P2〜)</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>初年度無料 (P3〜)</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/月 (P4〜)</t>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>既存 (優先送客対象)</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/件</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>¥150,000/本 (P2〜)</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>¥30,000/月 (P3〜)</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>(既存10社 #9)</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>2026-04-XX</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>既存優遇</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/件 (P2〜)</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>¥75,000/本 (P2〜)</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>初年度無料 (P3〜)</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/月 (P4〜)</t>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>既存 (優先送客対象)</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/件</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>¥150,000/本 (P2〜)</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>¥30,000/月 (P3〜)</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>(既存10社 #10)</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>2026-04-XX</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>既存優遇</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/件 (P2〜)</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>¥75,000/本 (P2〜)</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>初年度無料 (P3〜)</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>¥25,000/月 (P4〜)</t>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>既存 (優先送客対象)</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/件</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>¥150,000/本 (P2〜)</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>¥30,000/月 (P3〜)</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
@@ -3214,22 +2808,17 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>¥150,000/本 (P2〜)</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>¥150,000/本</t>
+          <t>¥30,000/月 (P3〜)</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>¥30,000/月</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>¥50,000/月</t>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
@@ -3255,22 +2844,17 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>¥150,000/本 (P2〜)</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>¥150,000/本</t>
+          <t>¥30,000/月 (P3〜)</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>¥30,000/月</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>¥50,000/月</t>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
@@ -3296,22 +2880,17 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>¥150,000/本 (P2〜)</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>¥150,000/本</t>
+          <t>¥30,000/月 (P3〜)</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>¥30,000/月</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>¥50,000/月</t>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
@@ -3337,22 +2916,17 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>¥150,000/本 (P2〜)</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>¥150,000/本</t>
+          <t>¥30,000/月 (P3〜)</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>¥30,000/月</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>¥50,000/月</t>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
@@ -3378,29 +2952,24 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>¥150,000/本 (P2〜)</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>¥150,000/本</t>
+          <t>¥30,000/月 (P3〜)</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>¥30,000/月</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>¥50,000/月</t>
+          <t>¥50,000/月 (P4〜)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3458,110 +3027,110 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>P0→P1</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>17公開ページ200・40+非公開404・10社と書面締結</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>17公開ページ200・40+非公開404・10社と書面締結 (¥50,000/件)</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>プレスリリース準備完了</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>P1→P2</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>見学会予約が2ヶ月連続で月5件以上</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>10社のうち8社がPhase2プランに興味あり</t>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>見学会予約が2ヶ月連続で月10件以上</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>10社のうち8社が撮影プランに興味あり</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>P2→P3</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>撮影プラン申込が2ヶ月で5本以上、見学会予約が月15件以上</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>記事/ニュースCMSが安定稼働</t>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>撮影プラン申込が2ヶ月で3本以上、見学会予約が月20件以上</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>記事/ニュースCMSが安定稼働、成果報酬トラッキング実装済み</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>P3→P4</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>2026-11-30</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>月額掲載の新規契約3社以上、総売上月50万円超</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>物件情報の登録が工務店から安定</t>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>月額掲載の契約5社以上、成果報酬が月1件以上発生、総売上月¥3,000,000 超</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>物件情報の登録が安定</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>P4→P5</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>2027-02-28</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>SaaSプラン契約10社以上、総売上月200万円超</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>SaaSプラン契約5社以上、総売上月¥7,000,000 超</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>全国展開の準備完了 (マーケ・採用計画)</t>
         </is>
@@ -3595,7 +3164,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⑥ プラン別 原価と粗利</t>
+          <t>⑥ プラン別 原価と粗利 (全員同一料金)</t>
         </is>
       </c>
     </row>
@@ -3634,189 +3203,189 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>見学会予約 (件あたり)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>¥50,000</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>¥5,000</t>
         </is>
       </c>
-      <c r="D5" s="12" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>¥45,000</t>
         </is>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>成果報酬 3% (¥3000万契約想定)</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>撮影プラン (本あたり)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>¥150,000</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>¥80,000</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>¥70,000</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>月額掲載 ベーシック</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>¥30,000</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>¥3,000</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>¥27,000</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>月額掲載 プロ</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>¥80,000</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>¥10,000</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>¥70,000</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>成果報酬 (¥3000万契約想定)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>¥900,000</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>¥20,000</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>¥880,000</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E9" s="11" t="inlineStr">
         <is>
           <t>98%</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>撮影プラン (本あたり)</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>SaaS ライト</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>¥50,000</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>¥8,000</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>¥42,000</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>SaaS プロ</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>¥150,000</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>¥80,000</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>¥70,000</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>月額掲載 ベーシック</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>¥30,000</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>¥3,000</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>¥27,000</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>月額掲載 プロ</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>¥80,000</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>¥10,000</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>¥70,000</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>SaaS ライト</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>¥50,000</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>¥8,000</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>¥42,000</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>SaaS プロ</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>¥150,000</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>¥30,000</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>¥120,000</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
